--- a/5module/Tables/Partners.xlsx
+++ b/5module/Tables/Partners.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5module\Ресурсы\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\PMPractice2\5module\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C815E72-E873-4331-A81F-22A931C4B446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3272A28E-6504-4104-AC8C-5F09EAFC76D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{EA5EE4C5-0F5B-44AA-B29A-91D715FA43DD}"/>
   </bookViews>
@@ -34,14 +34,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Наименование партнера</t>
   </si>
   <si>
-    <t>Директор</t>
-  </si>
-  <si>
     <t>Электронная почта партнера</t>
   </si>
   <si>
@@ -102,52 +99,10 @@
     <t>id партнера</t>
   </si>
   <si>
-    <t>Иванова</t>
-  </si>
-  <si>
-    <t>Александра</t>
-  </si>
-  <si>
-    <t>Ивановна</t>
-  </si>
-  <si>
-    <t>Петров</t>
-  </si>
-  <si>
-    <t>Василий</t>
-  </si>
-  <si>
-    <t>Петрович</t>
-  </si>
-  <si>
-    <t>Соловьев</t>
-  </si>
-  <si>
-    <t>Андрей</t>
-  </si>
-  <si>
-    <t>Николаевич</t>
-  </si>
-  <si>
-    <t>Воробьева</t>
-  </si>
-  <si>
-    <t>Екатерина</t>
-  </si>
-  <si>
-    <t>Валерьевна</t>
-  </si>
-  <si>
-    <t>Степанов</t>
-  </si>
-  <si>
-    <t>Степан</t>
-  </si>
-  <si>
-    <t>Сергеевич</t>
-  </si>
-  <si>
     <t>id Юридический адрес партнера</t>
+  </si>
+  <si>
+    <t>Директор id</t>
   </si>
 </sst>
 </file>
@@ -511,7 +466,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6CDA408F-FC27-4CCA-8A11-BFC624A7E7E0}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.81640625" customWidth="1"/>
@@ -524,199 +479,169 @@
     <col min="8" max="8" width="29.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" t="s">
         <v>1</v>
       </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
       <c r="F1" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="G1" t="s">
         <v>3</v>
       </c>
       <c r="H1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" t="s">
-        <v>5</v>
-      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
       <c r="E2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G2" t="s">
-        <v>8</v>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>2222455179</v>
       </c>
       <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>2222455179</v>
-      </c>
-      <c r="J2">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>26</v>
+        <v>18</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G3" t="s">
-        <v>10</v>
+      <c r="F3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>3333888520</v>
       </c>
       <c r="H3">
-        <v>2</v>
-      </c>
-      <c r="I3">
-        <v>3333888520</v>
-      </c>
-      <c r="J3">
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
       <c r="E4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G4" t="s">
-        <v>13</v>
+      <c r="F4">
+        <v>3</v>
+      </c>
+      <c r="G4">
+        <v>4440391035</v>
       </c>
       <c r="H4">
-        <v>3</v>
-      </c>
-      <c r="I4">
-        <v>4440391035</v>
-      </c>
-      <c r="J4">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>32</v>
-      </c>
       <c r="E5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="G5" t="s">
-        <v>16</v>
+      <c r="F5">
+        <v>4</v>
+      </c>
+      <c r="G5">
+        <v>1111520857</v>
       </c>
       <c r="H5">
-        <v>4</v>
-      </c>
-      <c r="I5">
-        <v>1111520857</v>
-      </c>
-      <c r="J5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D6" t="s">
-        <v>35</v>
+        <v>19</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G6" t="s">
-        <v>18</v>
+      <c r="F6">
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <v>5552431140</v>
       </c>
       <c r="H6">
-        <v>5</v>
-      </c>
-      <c r="I6">
-        <v>5552431140</v>
-      </c>
-      <c r="J6">
         <v>10</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" xr:uid="{F9D58CB7-B0CB-429F-A2F2-6D683C38665A}"/>
-    <hyperlink ref="F3" r:id="rId2" xr:uid="{4AF94106-B754-4056-A498-3BC69160E765}"/>
-    <hyperlink ref="F4" r:id="rId3" xr:uid="{E6A8F9EE-FCC3-4219-8C66-47F6F4BBD195}"/>
-    <hyperlink ref="F6" r:id="rId4" xr:uid="{68C291C3-2BB4-4259-B236-012039853E00}"/>
-    <hyperlink ref="F5" r:id="rId5" xr:uid="{313A085D-95E8-4D53-BA72-B2179A489583}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{F9D58CB7-B0CB-429F-A2F2-6D683C38665A}"/>
+    <hyperlink ref="D3" r:id="rId2" xr:uid="{4AF94106-B754-4056-A498-3BC69160E765}"/>
+    <hyperlink ref="D4" r:id="rId3" xr:uid="{E6A8F9EE-FCC3-4219-8C66-47F6F4BBD195}"/>
+    <hyperlink ref="D6" r:id="rId4" xr:uid="{68C291C3-2BB4-4259-B236-012039853E00}"/>
+    <hyperlink ref="D5" r:id="rId5" xr:uid="{313A085D-95E8-4D53-BA72-B2179A489583}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
